--- a/output/pdf_financials_xlsx/EXCL.xlsx
+++ b/output/pdf_financials_xlsx/EXCL.xlsx
@@ -637,10 +637,10 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.002913</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.017571</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -917,10 +917,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.205365</v>
+        <v>-0.208278</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-1.783911</v>
+        <v>-1.801482</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -953,10 +953,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.205365</v>
+        <v>-0.208278</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-1.783911</v>
+        <v>-1.801482</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1040,10 +1040,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.038183</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>1.61085</v>
       </c>
       <c r="D34" s="1" t="inlineStr">
         <is>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.038183</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>1.61085</v>
       </c>
       <c r="D36" s="1" t="inlineStr">
         <is>
@@ -3105,7 +3105,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">

--- a/output/pdf_financials_xlsx/EXCL.xlsx
+++ b/output/pdf_financials_xlsx/EXCL.xlsx
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D67" s="1" t="inlineStr">
         <is>
@@ -1664,10 +1664,10 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="D68" s="1" t="inlineStr">
         <is>
@@ -2222,15 +2222,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.205365</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-1.783911</v>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
@@ -2244,15 +2240,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -2266,15 +2258,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
@@ -2288,15 +2276,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
@@ -2310,15 +2294,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.157197</v>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
@@ -2332,15 +2312,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.091609</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>-0.060529</v>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
@@ -2354,15 +2330,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
@@ -2376,15 +2348,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.092609</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>-0.217726</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
@@ -2398,15 +2366,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0.025649</v>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
@@ -2420,15 +2384,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
@@ -2442,15 +2402,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
@@ -2464,15 +2420,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
@@ -2486,15 +2438,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
@@ -2508,15 +2456,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
@@ -2530,15 +2474,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
@@ -2552,15 +2492,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
@@ -2574,15 +2510,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
@@ -2596,15 +2528,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
@@ -2618,15 +2546,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
@@ -2640,15 +2564,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>-0.016506</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>-0.04</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
@@ -2662,15 +2582,11 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>-0.016506</v>
+      </c>
+      <c r="C119" s="3" t="n">
+        <v>0.132218</v>
       </c>
       <c r="D119" s="1" t="inlineStr">
         <is>
@@ -2684,15 +2600,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
@@ -2706,15 +2618,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
@@ -2728,15 +2636,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
@@ -2750,15 +2654,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
@@ -2772,15 +2672,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
@@ -2794,15 +2690,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
@@ -2816,15 +2708,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
@@ -2860,15 +2748,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>-0.15592</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
@@ -2882,15 +2766,11 @@
           <t>Cash Flow from Financing</t>
         </is>
       </c>
-      <c r="B129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C129" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B129" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C129" s="3" t="n">
+        <v>2.518955</v>
       </c>
       <c r="D129" s="1" t="inlineStr">
         <is>
@@ -2904,15 +2784,11 @@
           <t xml:space="preserve">  Beginning Cash Position</t>
         </is>
       </c>
-      <c r="B130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C130" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B130" s="3" t="n">
+        <v>0.135939</v>
+      </c>
+      <c r="C130" s="3" t="n">
+        <v>0.038183</v>
       </c>
       <c r="D130" s="1" t="inlineStr">
         <is>
@@ -2926,15 +2802,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
@@ -2948,15 +2820,11 @@
           <t xml:space="preserve">  Net Change in Cash</t>
         </is>
       </c>
-      <c r="B132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B132" s="3" t="n">
+        <v>-0.097756</v>
+      </c>
+      <c r="C132" s="3" t="n">
+        <v>1.572667</v>
       </c>
       <c r="D132" s="1" t="inlineStr">
         <is>
@@ -2970,15 +2838,11 @@
           <t>Ending Cash Position</t>
         </is>
       </c>
-      <c r="B133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C133" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B133" s="3" t="n">
+        <v>0.038183</v>
+      </c>
+      <c r="C133" s="3" t="n">
+        <v>1.61085</v>
       </c>
       <c r="D133" s="1" t="inlineStr">
         <is>
@@ -2992,15 +2856,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
@@ -3014,15 +2874,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.08125</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-1.078506</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -3041,7 +2897,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3404,25 +3260,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>OPERATING ACTIVITIES</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Exploration and evaluation (note 5) $</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr"/>
+          <t>Loss for the year $</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E12" s="5" t="n">
-        <v>0.041024</v>
+        <v>-0.205365</v>
       </c>
       <c r="F12" s="5" t="n">
-        <v>0.297325</v>
+        <v>-1.783911</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -3433,29 +3293,27 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>General and administration (notes 7 and 9)</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="n">
-        <v>0.13553</v>
+          <t>Listing expenses</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F13" s="5" t="n">
-        <v>0.618167</v>
+        <v>0.822482</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -3466,31 +3324,27 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sales and marketing</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>SellingAndMarketingExpense</t>
-        </is>
-      </c>
+          <t>Shares issued for services</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F14" s="5" t="n">
-        <v>0.0301</v>
+        <v>0.075</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -3501,27 +3355,27 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Share-based compensation (note 8)</t>
+          <t>Impairment of property</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="n">
-        <v>0.025649</v>
+      <c r="E15" s="5" t="n">
+        <v>0.031506</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -3532,29 +3386,31 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>EXPENSES</t>
+          <t>Items not affecting cash</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>EXPENSES total</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E16" s="5" t="n">
-        <v>0.176554</v>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F16" s="5" t="n">
-        <v>0.971241</v>
+        <v>0.025649</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -3565,27 +3421,31 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Listing expense (note 3)</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="n">
-        <v>-0.822482</v>
+          <t>Amounts receivable</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -3596,27 +3456,31 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Impairment on property (note 5)</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" s="5" t="n">
-        <v>-0.031506</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Prepaids</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-0.157197</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -3627,29 +3491,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Accounts payable and accrued liabilities</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E19" s="5" t="n">
-        <v>0.002913</v>
+        <v>0.091609</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.017571</v>
+        <v>-0.060529</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -3660,29 +3524,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>Net change in non-cash working capital items</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Cash used in operating activities</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>OperatingCashFlow</t>
         </is>
       </c>
       <c r="E20" s="5" t="n">
-        <v>-0.000218</v>
+        <v>-0.08125</v>
       </c>
       <c r="F20" s="5" t="n">
-        <v>-0.007759</v>
+        <v>-1.078506</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -3693,29 +3557,27 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>-0.205365</v>
+          <t>Cash acquired in reverse takeover transaction</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F21" s="5" t="n">
-        <v>-1.783911</v>
+        <v>0.172218</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -3726,29 +3588,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OTHER ITEMS</t>
+          <t>INVESTING ACTIVITIES</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Basic and diluted loss per common share $</t>
+          <t>Acquisition of exploration and evaluation assets</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>NetOtherInvestingChanges</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>-1e-08</v>
+        <v>-0.016506</v>
       </c>
       <c r="F22" s="5" t="n">
-        <v>-5.999999999999999e-08</v>
+        <v>-0.04</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -3759,27 +3621,706 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>INVESTING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cash used in investing activities</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>InvestingCashFlow</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-0.016506</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>0.132218</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Issuance of common shares</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>2.674875</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Share issuance costs</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NetOtherFinancingCharges</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-0.15592</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Cash provided by financing activities</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>2.518955</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Net change in cash</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-0.097756</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>1.572667</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Cash, beginning of the year</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>BeginningCashPosition</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>0.135939</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>0.038183</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Cash, end of the year $</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>EndCashPosition</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>0.038183</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>1.61085</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>TOTAL 129,254 (205,365) (76,111) 982,200 2,439,875 235,000 75,000 (155,920) 25,649 25,000</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" s="5" t="n">
+        <v>1.766782</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-1.783911</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>FINANCING ACTIVITIES</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>DEFICIT (129,496) (205,365) (334,861) - - - - - - -</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" s="5" t="n">
+        <v>-2.118772</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>-1.783911</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>cash_flow</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>-      - - -                                                           of</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>OF part SHARES 20,730,000 20,730,000 6,388,000 16,265,830 1,566,666 500,000</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" s="5" t="n">
+        <v>45.617163</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>0.166667</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>income_statement</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Exploration and evaluation (note 5) $</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" s="5" t="n">
+        <v>0.041024</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>0.297325</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>General and administration (notes 7 and 9)</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.13553</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>0.618167</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Sales and marketing</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>0.0301</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 8)</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>0.025649</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>EXPENSES</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>EXPENSES total</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>0.176554</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>0.971241</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Listing expense (note 3)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-0.822482</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Impairment on property (note 5)</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>-0.031506</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>0.002913</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>0.017571</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>-0.000218</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>-0.007759</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>LOSS AND COMPREHENSIVE LOSS FOR THE YEAR</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>-0.205365</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>-1.783911</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>OTHER ITEMS</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Basic and diluted loss per common share $</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>-1e-08</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>-5.999999999999999e-08</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
         <is>
           <t>Weighted average number of common shares</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
+      <c r="C44" t="inlineStr">
         <is>
           <t>Weighted average number of common shares outstanding – basic and diluted</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" s="5" t="n">
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
         <v>20.73</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F44" s="5" t="n">
         <v>29.22637</v>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>-</t>
         </is>
